--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3041-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3041-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{974F0A17-438D-47F3-9850-BEFA5EC31AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{987EFEA4-C830-4739-BFB3-F72743307FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{1BD7C7A5-2AE6-47B6-A8B0-AF18F096CF38}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{EC797CB2-A1BE-4BD2-B260-7660E124E18A}"/>
   </bookViews>
   <sheets>
     <sheet name="3041-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1463,24 +1463,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF348ECE-4D90-4FBB-815E-B81FE1789391}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759ED5AC-85C4-4AC2-AC84-33C85B1502F1}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="5.109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="1" max="2" width="6.5" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1508,7 +1508,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1634,7 +1634,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="38">
         <v>2023</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="40">
         <v>2022</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>25</v>
       </c>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="38">
         <v>2021</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="40">
         <v>2020</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2019</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="40">
         <v>2018</v>
       </c>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="38">
         <v>2017</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2016</v>
       </c>
@@ -2846,7 +2846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="38">
         <v>2015</v>
       </c>
@@ -2900,7 +2900,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="40">
         <v>2014</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2013</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="40">
         <v>2012</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="38">
         <v>2011</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>8.56</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2010</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="38">
         <v>2009</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="40">
         <v>2008</v>
       </c>
@@ -3278,7 +3278,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2007</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="40">
         <v>2006</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="38">
         <v>2005</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2004</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="38">
         <v>2003</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="40">
         <v>2002</v>
       </c>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2001</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="40">
         <v>2000</v>
       </c>
@@ -3710,7 +3710,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="38">
         <v>1999</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>1998</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="38">
         <v>1997</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="40">
         <v>1996</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>1995</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="40" t="s">
         <v>39</v>
       </c>
